--- a/data/trans_orig/P2C_R1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275719</t>
+          <t>276528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196333</t>
+          <t>194835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205309</t>
+          <t>205327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>476076</t>
+          <t>475561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485932</t>
+          <t>485934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>182758</t>
+          <t>182616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194908</t>
+          <t>194866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216063</t>
+          <t>216573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402562</t>
+          <t>403126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417153</t>
+          <t>417094</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>333266</t>
+          <t>333040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120828</t>
+          <t>120350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>456881</t>
+          <t>456469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>464462</t>
+          <t>464452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>770278</t>
+          <t>769333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>453745</t>
+          <t>453867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466786</t>
+          <t>467228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1226439</t>
+          <t>1227202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1242010</t>
+          <t>1242262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -2105,97 +2105,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207199</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>403718</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>405731</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>610943</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>612931</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2281</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1879</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6759</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2281</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8121</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>7454</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2281</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106843</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>860500</t>
+          <t>861862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>967363</t>
+          <t>968010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28867</t>
+          <t>29697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>41315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1887658</t>
+          <t>1888230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1903172</t>
+          <t>1902879</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2271422</t>
+          <t>2270592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2289830</t>
+          <t>2289840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4166844</t>
+          <t>4167171</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4189540</t>
+          <t>4189994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>26189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238532</t>
+          <t>239589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252237</t>
+          <t>252275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189969</t>
+          <t>190349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203694</t>
+          <t>203723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>435667</t>
+          <t>435820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>453188</t>
+          <t>453306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,47 +3761,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>4976</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>13713</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>4976</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>12661</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>260579</t>
+          <t>259840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228996</t>
+          <t>228903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236252</t>
+          <t>236235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,47 +3874,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>502467</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>493730</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>505522</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>99,62%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>502467</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>494782</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>506365</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399549</t>
+          <t>399927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>407096</t>
+          <t>407942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177133</t>
+          <t>177675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>581070</t>
+          <t>580921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589952</t>
+          <t>589964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>773867</t>
+          <t>775065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>505613</t>
+          <t>506233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>519673</t>
+          <t>518845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1284670</t>
+          <t>1285374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1298541</t>
+          <t>1298555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16932</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>312555</t>
+          <t>312605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>571852</t>
+          <t>572710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>583988</t>
+          <t>583833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>889363</t>
+          <t>890664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>903044</t>
+          <t>902849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>764198</t>
+          <t>764487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>774139</t>
+          <t>774130</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868262</t>
+          <t>868110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>876970</t>
+          <t>876968</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40394</t>
+          <t>42406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33055</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63576</t>
+          <t>62434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2110561</t>
+          <t>2108907</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2127869</t>
+          <t>2127599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2469330</t>
+          <t>2467318</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2490721</t>
+          <t>2491085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4583474</t>
+          <t>4584616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4613995</t>
+          <t>4613728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208971</t>
+          <t>209386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218112</t>
+          <t>218087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193225</t>
+          <t>192939</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203862</t>
+          <t>203776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>407075</t>
+          <t>407686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>420027</t>
+          <t>420158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220032</t>
+          <t>220437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227874</t>
+          <t>227892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232057</t>
+          <t>232997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242537</t>
+          <t>242534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>457818</t>
+          <t>457874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469434</t>
+          <t>469447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321569</t>
+          <t>320283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329476</t>
+          <t>329474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120412</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122528</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>443794</t>
+          <t>444375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452007</t>
+          <t>452003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625861</t>
+          <t>626197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635788</t>
+          <t>635792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>515279</t>
+          <t>514303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>521673</t>
+          <t>521669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1145674</t>
+          <t>1143744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1156460</t>
+          <t>1156387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368293</t>
+          <t>367654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>374944</t>
+          <t>374933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489762</t>
+          <t>489569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>499073</t>
+          <t>499037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>861185</t>
+          <t>861682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>872839</t>
+          <t>872913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102784</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>717855</t>
+          <t>718772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>728433</t>
+          <t>728445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>822475</t>
+          <t>823320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>833267</t>
+          <t>833425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>27270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33959</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>28878</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55169</t>
+          <t>55665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1867385</t>
+          <t>1868526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1885307</t>
+          <t>1885484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2291166</t>
+          <t>2290986</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2310946</t>
+          <t>2310652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4165752</t>
+          <t>4165256</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4193019</t>
+          <t>4192043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>25823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>57679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57192</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67431</t>
+          <t>67014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108542</t>
+          <t>108319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122483</t>
+          <t>122802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>46142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54792</t>
+          <t>54605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59230</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99683</t>
+          <t>99806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112196</t>
+          <t>112396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63180</t>
+          <t>63312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75414</t>
+          <t>74847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26648</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84182</t>
+          <t>85159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98965</t>
+          <t>99286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44978</t>
+          <t>45367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39590</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84815</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132506</t>
+          <t>132117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152928</t>
+          <t>152616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>299258</t>
+          <t>298818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>335902</t>
+          <t>335222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431517</t>
+          <t>431314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>500384</t>
+          <t>497734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25877</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40273</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36902</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56481</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51548</t>
+          <t>52325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63805</t>
+          <t>64073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141452</t>
+          <t>141106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155848</t>
+          <t>155838</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197485</t>
+          <t>197238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217064</t>
+          <t>216440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52915</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>36930</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60136</t>
+          <t>57693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142756</t>
+          <t>142201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>160661</t>
+          <t>160149</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153075</t>
+          <t>155518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>175183</t>
+          <t>176281</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65927</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94730</t>
+          <t>94704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>53687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159121</t>
+          <t>158506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116066</t>
+          <t>116199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>239701</t>
+          <t>237819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376446</t>
+          <t>376472</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>405249</t>
+          <t>407231</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>726486</t>
+          <t>727101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>827193</t>
+          <t>831920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1117082</t>
+          <t>1118964</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1240717</t>
+          <t>1240584</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276528</t>
+          <t>275583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194835</t>
+          <t>196097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205327</t>
+          <t>205308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>475561</t>
+          <t>475544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485934</t>
+          <t>485818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>182616</t>
+          <t>182696</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194866</t>
+          <t>194895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216573</t>
+          <t>216376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403126</t>
+          <t>403614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417094</t>
+          <t>417273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>333040</t>
+          <t>332923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>120312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>456469</t>
+          <t>457090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>464452</t>
+          <t>464462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>769333</t>
+          <t>770297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>453867</t>
+          <t>453653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>467228</t>
+          <t>466634</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1227202</t>
+          <t>1227677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1242262</t>
+          <t>1242722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>861862</t>
+          <t>861064</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>968010</t>
+          <t>966713</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41315</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1888230</t>
+          <t>1887756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1902879</t>
+          <t>1902208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2270592</t>
+          <t>2271722</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2289840</t>
+          <t>2289915</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4167171</t>
+          <t>4166182</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4189994</t>
+          <t>4190202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26189</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239589</t>
+          <t>239173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252275</t>
+          <t>252323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>190349</t>
+          <t>191726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203723</t>
+          <t>203814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>435820</t>
+          <t>435611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>453306</t>
+          <t>453240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>259840</t>
+          <t>259855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228903</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236235</t>
+          <t>236261</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>493730</t>
+          <t>493485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505522</t>
+          <t>505679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399927</t>
+          <t>400076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>407942</t>
+          <t>407964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177675</t>
+          <t>176669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580921</t>
+          <t>580850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589964</t>
+          <t>589947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>775065</t>
+          <t>775374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>506233</t>
+          <t>506555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>518845</t>
+          <t>518967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1285374</t>
+          <t>1284610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1298555</t>
+          <t>1298591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,47 +4790,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>8018</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>3218</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>16297</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>8018</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>15631</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>312605</t>
+          <t>313607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>572710</t>
+          <t>571890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>583833</t>
+          <t>583868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,47 +4903,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>898277</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>889998</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>903077</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,64%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>841</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>898277</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>890664</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>902849</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>764487</t>
+          <t>764534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>774130</t>
+          <t>774145</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868110</t>
+          <t>867234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>876968</t>
+          <t>876952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>41903</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>32772</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62434</t>
+          <t>62826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2108907</t>
+          <t>2109471</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2127599</t>
+          <t>2127848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2467318</t>
+          <t>2467821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2491085</t>
+          <t>2491264</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4584616</t>
+          <t>4584224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4613728</t>
+          <t>4614278</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209386</t>
+          <t>209440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218087</t>
+          <t>218101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192939</t>
+          <t>193476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203776</t>
+          <t>203840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>407686</t>
+          <t>407618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>420158</t>
+          <t>420132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220437</t>
+          <t>220201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227892</t>
+          <t>227879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232997</t>
+          <t>231822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242534</t>
+          <t>242537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>457874</t>
+          <t>458394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469447</t>
+          <t>469618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>320283</t>
+          <t>321541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329474</t>
+          <t>329455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>444375</t>
+          <t>443435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452003</t>
+          <t>452001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626197</t>
+          <t>626871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635792</t>
+          <t>635795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>514303</t>
+          <t>514813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>521669</t>
+          <t>521680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1143744</t>
+          <t>1145121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1156387</t>
+          <t>1156731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>367654</t>
+          <t>367778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>374933</t>
+          <t>374948</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489569</t>
+          <t>489747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>499037</t>
+          <t>499026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>861682</t>
+          <t>862076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>872913</t>
+          <t>872954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>718772</t>
+          <t>718205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>728445</t>
+          <t>728424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>823320</t>
+          <t>823437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>833425</t>
+          <t>833409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>29707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55665</t>
+          <t>56872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1868526</t>
+          <t>1868278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1885484</t>
+          <t>1885510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2290986</t>
+          <t>2290890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2310652</t>
+          <t>2310885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4165256</t>
+          <t>4164049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4192043</t>
+          <t>4191214</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>61817</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>55960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>65820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63292</t>
+          <t>70490</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>63735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67014</t>
+          <t>74640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>117197</t>
+          <t>132307</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108319</t>
+          <t>124652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122802</t>
+          <t>138503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>79808</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>79808</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>79808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>134142</t>
+          <t>149985</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>134142</t>
+          <t>149985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>134142</t>
+          <t>149985</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>57847</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46142</t>
+          <t>52819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>61477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>55564</t>
+          <t>63033</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59314</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>106730</t>
+          <t>120880</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99806</t>
+          <t>113316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112396</t>
+          <t>126260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58130</t>
+          <t>64792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58130</t>
+          <t>64792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58130</t>
+          <t>64792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65810</t>
+          <t>74552</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65810</t>
+          <t>74552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65810</t>
+          <t>74552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>123940</t>
+          <t>139344</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123940</t>
+          <t>139344</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>123940</t>
+          <t>139344</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>24666</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69959</t>
+          <t>81609</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63312</t>
+          <t>74431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74847</t>
+          <t>86712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>92761</t>
+          <t>106583</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85159</t>
+          <t>96241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99286</t>
+          <t>112913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>95485</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>95485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>95485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>131249</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>131249</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>131249</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33318</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45367</t>
+          <t>49827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47612</t>
+          <t>52065</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>40146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85018</t>
+          <t>66272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>144166</t>
+          <t>170359</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132117</t>
+          <t>156227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152616</t>
+          <t>179958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>324554</t>
+          <t>135997</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298818</t>
+          <t>129605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>335222</t>
+          <t>140682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>468720</t>
+          <t>306356</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431314</t>
+          <t>292149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>497734</t>
+          <t>318275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177484</t>
+          <t>206054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177484</t>
+          <t>206054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>177484</t>
+          <t>206054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338848</t>
+          <t>152367</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>338848</t>
+          <t>152367</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>338848</t>
+          <t>152367</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>516332</t>
+          <t>358421</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>516332</t>
+          <t>358421</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>516332</t>
+          <t>358421</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>34354</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>27287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40619</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>46059</t>
+          <t>47912</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>58840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58893</t>
+          <t>68053</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>60845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>73289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>149014</t>
+          <t>175811</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141106</t>
+          <t>168060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155838</t>
+          <t>182878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>207907</t>
+          <t>243865</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197238</t>
+          <t>232937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216440</t>
+          <t>253214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>86,78%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>81612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>81612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>81612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>181725</t>
+          <t>210165</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>181725</t>
+          <t>210165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181725</t>
+          <t>210165</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>253966</t>
+          <t>291777</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>253966</t>
+          <t>291777</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>253966</t>
+          <t>291777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42913</t>
+          <t>45747</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34967</t>
+          <t>37029</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>56178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>49707</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36930</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57693</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>23819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>152203</t>
+          <t>175856</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142201</t>
+          <t>165425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>160149</t>
+          <t>184574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>166509</t>
+          <t>196332</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155518</t>
+          <t>182988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176281</t>
+          <t>204978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>195116</t>
+          <t>221603</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>195116</t>
+          <t>221603</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>195116</t>
+          <t>221603</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>213211</t>
+          <t>246039</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>213211</t>
+          <t>246039</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>213211</t>
+          <t>246039</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>82394</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63945</t>
+          <t>67444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94704</t>
+          <t>100174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>118178</t>
+          <t>128099</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53687</t>
+          <t>113138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158506</t>
+          <t>144876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>196959</t>
+          <t>210492</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116199</t>
+          <t>189635</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>237819</t>
+          <t>234836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>392395</t>
+          <t>460161</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376472</t>
+          <t>442381</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407231</t>
+          <t>475111</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>767429</t>
+          <t>646161</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>727101</t>
+          <t>629384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>831920</t>
+          <t>661122</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1159824</t>
+          <t>1106323</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1118964</t>
+          <t>1081979</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1240584</t>
+          <t>1127180</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>471176</t>
+          <t>542555</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>471176</t>
+          <t>542555</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>471176</t>
+          <t>542555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>885607</t>
+          <t>774260</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>885607</t>
+          <t>774260</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>885607</t>
+          <t>774260</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1356783</t>
+          <t>1316815</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1356783</t>
+          <t>1316815</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1356783</t>
+          <t>1316815</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
